--- a/schemas/single_cell/singlecell_schema_main_v0.4.xlsx
+++ b/schemas/single_cell/singlecell_schema_main_v0.4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/providen/Documents/EI/Projects/COPO-schemas/single_cell/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82992FDF-4828-5E4A-9195-C924823E24B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3E9841-8636-BD49-912D-441E57B94B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30240" yWindow="-2660" windowWidth="38400" windowHeight="21600" activeTab="1" xr2:uid="{7BD8D0E6-E1F4-E04F-9790-31602B31B6DB}"/>
+    <workbookView xWindow="37020" yWindow="-140" windowWidth="27740" windowHeight="16420" activeTab="5" xr2:uid="{7BD8D0E6-E1F4-E04F-9790-31602B31B6DB}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3128" uniqueCount="1272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3132" uniqueCount="1278">
   <si>
     <t>component_name</t>
   </si>
@@ -4029,6 +4029,24 @@
   </si>
   <si>
     <t>NOMe-Seq</t>
+  </si>
+  <si>
+    <t>^\d{4}-\d{4}-\d{4}-\d{3}[\dX]$</t>
+  </si>
+  <si>
+    <t>^((https?|ftp):\/\/[^\s|]+)(\|((https?|ftp):\/\/[^\s|]+))*$</t>
+  </si>
+  <si>
+    <t>Expected a URL starting with 'http', 'https' or 'ftp'. For multiple URLs, separate them using the pipe symbol (|) with no spaces. e.g. https://reference-genome-example.com|https://example.org</t>
+  </si>
+  <si>
+    <t>Expected positive whole numbers or decimal numbers.</t>
+  </si>
+  <si>
+    <t>AND(LEN(A1)=19,MID(A1,5,1)="-",MID(A1,10,1)="-",MID(A1,15,1)="-",ISNUMBER(--LEFT(A1,4)),ISNUMBER(--MID(A1,6,4)),ISNUMBER(--MID(A1,11,4)),ISNUMBER(--MID(A1,16,3)),OR(ISNUMBER(--RIGHT(A1,1)),RIGHT(A1,1)="X"))</t>
+  </si>
+  <si>
+    <t>OR(LEFT(A1,7)="http://",LEFT(A1,8)="https://",LEFT(A1,6)="ftp://")</t>
   </si>
 </sst>
 </file>
@@ -4749,7 +4767,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5009,9 +5027,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -6249,7 +6264,7 @@
         <v>110</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>111</v>
+        <v>1272</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>1223</v>
@@ -8543,10 +8558,10 @@
         <v>290</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>241</v>
+        <v>676</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>1226</v>
+        <v>1275</v>
       </c>
       <c r="M68" s="3" t="s">
         <v>24</v>
@@ -13398,7 +13413,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="176" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="8" t="s">
         <v>1103</v>
       </c>
@@ -13467,7 +13482,7 @@
       <c r="I177" s="3" t="s">
         <v>1123</v>
       </c>
-      <c r="J177" s="97" t="s">
+      <c r="J177" s="68" t="s">
         <v>1165</v>
       </c>
       <c r="M177" s="3" t="s">
@@ -13512,10 +13527,10 @@
         <v>1235</v>
       </c>
       <c r="K178" s="3" t="s">
-        <v>201</v>
+        <v>1273</v>
       </c>
       <c r="L178" s="3" t="s">
-        <v>1228</v>
+        <v>1274</v>
       </c>
       <c r="M178" s="3" t="s">
         <v>24</v>
@@ -13802,7 +13817,7 @@
       <c r="J185" s="95">
         <v>2.5</v>
       </c>
-      <c r="K185" s="98" t="s">
+      <c r="K185" s="97" t="s">
         <v>1252</v>
       </c>
       <c r="L185" t="s">
@@ -14626,6 +14641,7 @@
     <hyperlink ref="J178" r:id="rId59" xr:uid="{36FAB4CA-D2E7-2648-850A-DCF88860F33D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId60"/>
 </worksheet>
 </file>
@@ -26514,7 +26530,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="41.5" style="19" customWidth="1"/>
@@ -27127,7 +27143,7 @@
       </c>
       <c r="C61" s="50"/>
     </row>
-    <row r="62" spans="1:3" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="49" t="s">
         <v>1208</v>
       </c>
@@ -27135,6 +27151,24 @@
         <v>1258</v>
       </c>
       <c r="C62" s="50"/>
+    </row>
+    <row r="63" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="49" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B63" s="49" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C63" s="50"/>
+    </row>
+    <row r="64" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="49" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B64" s="49" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C64" s="50"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C53" xr:uid="{D95B3E19-31EE-401E-8E14-DBEF7BC74F95}"/>
